--- a/static/standards-correlations/Kansas_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Kansas_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$38</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Kansas Model Standards, adopted April 2019</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Kansas Model Standards, adopted April 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1658,7 +1659,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Unit 5.3 teaches version control, repositories, and commits directly. Discovery Systems 13 and 14 assign team roles and manage a project timeline.</t>
+          <t>Unit 5.3 teaches version control, repositories, and commits directly. Introductory Systems 13 and 14 assign team roles and manage a project timeline.</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1929,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3H (Find the Community) has students find real public repositories from practitioners and hobbyists, and Discovery Coding 2 covers how professional programmers actually spend their time. Local industry is not surveyed.</t>
+          <t>Ext 5.3H (Find the Community) has students find real public repositories from practitioners and hobbyists, and Introductory Coding 2 covers how professional programmers actually spend their time. Local industry is not surveyed.</t>
         </is>
       </c>
     </row>
@@ -2193,6 +2194,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2237,7 +2239,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2251,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2351,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -2366,7 +2370,7 @@
 NOTE: L1.CS.IO.01 contains a spelling error in the source ('efficeint'); corrected here to 'efficient'.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension so a reviewer can verify placement.</t>
         </is>
       </c>
